--- a/input/mapping/002. OCB_GOLD_TCKH_V_BRANCH_LIST_HOP.xlsx
+++ b/input/mapping/002. OCB_GOLD_TCKH_V_BRANCH_LIST_HOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30410"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1681" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97B79D36-8BFC-4368-B377-04B8B94E7200}"/>
+  <xr:revisionPtr revIDLastSave="1683" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60F48F75-B12D-4802-9031-45C393D538DB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="15" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -3483,6 +3483,12 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="48" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3761,12 +3767,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
@@ -3789,7 +3789,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4158,19 +4158,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="30" customHeight="1">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="186" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
-      <c r="K1" s="186"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="188"/>
       <c r="L1" s="24"/>
       <c r="M1" s="24"/>
       <c r="N1" s="24"/>
@@ -4210,112 +4210,112 @@
       <c r="AV1" s="24"/>
     </row>
     <row r="2" spans="1:48" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="166" t="s">
+      <c r="A2" s="168" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="167"/>
-      <c r="C2" s="178" t="s">
+      <c r="B2" s="169"/>
+      <c r="C2" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="172" t="s">
+      <c r="D2" s="174" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="173"/>
-      <c r="F2" s="178" t="s">
+      <c r="E2" s="175"/>
+      <c r="F2" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="172" t="s">
+      <c r="G2" s="174" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="181"/>
-      <c r="I2" s="178" t="s">
+      <c r="H2" s="183"/>
+      <c r="I2" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="187" t="s">
+      <c r="J2" s="189" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="188"/>
+      <c r="K2" s="190"/>
     </row>
     <row r="3" spans="1:48">
-      <c r="A3" s="168"/>
-      <c r="B3" s="169"/>
-      <c r="C3" s="179"/>
-      <c r="D3" s="174"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="179"/>
-      <c r="G3" s="174"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="179"/>
-      <c r="J3" s="189"/>
-      <c r="K3" s="190"/>
+      <c r="A3" s="170"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="176"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="181"/>
+      <c r="G3" s="176"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="181"/>
+      <c r="J3" s="191"/>
+      <c r="K3" s="192"/>
     </row>
     <row r="4" spans="1:48">
-      <c r="A4" s="168"/>
-      <c r="B4" s="169"/>
-      <c r="C4" s="179"/>
-      <c r="D4" s="174"/>
-      <c r="E4" s="175"/>
-      <c r="F4" s="179"/>
-      <c r="G4" s="174"/>
-      <c r="H4" s="182"/>
-      <c r="I4" s="180"/>
-      <c r="J4" s="191"/>
-      <c r="K4" s="192"/>
+      <c r="A4" s="170"/>
+      <c r="B4" s="171"/>
+      <c r="C4" s="181"/>
+      <c r="D4" s="176"/>
+      <c r="E4" s="177"/>
+      <c r="F4" s="181"/>
+      <c r="G4" s="176"/>
+      <c r="H4" s="184"/>
+      <c r="I4" s="182"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="194"/>
     </row>
     <row r="5" spans="1:48">
-      <c r="A5" s="168"/>
-      <c r="B5" s="169"/>
-      <c r="C5" s="179"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="175"/>
-      <c r="F5" s="179"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="182"/>
+      <c r="A5" s="170"/>
+      <c r="B5" s="171"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="176"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="181"/>
+      <c r="G5" s="176"/>
+      <c r="H5" s="184"/>
       <c r="J5" s="109"/>
       <c r="K5" s="109"/>
     </row>
     <row r="6" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A6" s="168"/>
-      <c r="B6" s="169"/>
-      <c r="C6" s="179"/>
-      <c r="D6" s="174"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="179"/>
-      <c r="G6" s="174"/>
-      <c r="H6" s="182"/>
-      <c r="I6" s="178" t="s">
+      <c r="A6" s="170"/>
+      <c r="B6" s="171"/>
+      <c r="C6" s="181"/>
+      <c r="D6" s="176"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="181"/>
+      <c r="G6" s="176"/>
+      <c r="H6" s="184"/>
+      <c r="I6" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="193" t="s">
+      <c r="J6" s="195" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="194"/>
+      <c r="K6" s="196"/>
     </row>
     <row r="7" spans="1:48">
-      <c r="A7" s="168"/>
-      <c r="B7" s="169"/>
-      <c r="C7" s="179"/>
-      <c r="D7" s="174"/>
-      <c r="E7" s="175"/>
-      <c r="F7" s="179"/>
-      <c r="G7" s="174"/>
-      <c r="H7" s="182"/>
-      <c r="I7" s="179"/>
-      <c r="J7" s="195"/>
-      <c r="K7" s="196"/>
+      <c r="A7" s="170"/>
+      <c r="B7" s="171"/>
+      <c r="C7" s="181"/>
+      <c r="D7" s="176"/>
+      <c r="E7" s="177"/>
+      <c r="F7" s="181"/>
+      <c r="G7" s="176"/>
+      <c r="H7" s="184"/>
+      <c r="I7" s="181"/>
+      <c r="J7" s="197"/>
+      <c r="K7" s="198"/>
     </row>
     <row r="8" spans="1:48">
-      <c r="A8" s="170"/>
-      <c r="B8" s="171"/>
-      <c r="C8" s="180"/>
-      <c r="D8" s="176"/>
-      <c r="E8" s="177"/>
-      <c r="F8" s="180"/>
-      <c r="G8" s="176"/>
-      <c r="H8" s="183"/>
-      <c r="I8" s="180"/>
-      <c r="J8" s="197"/>
-      <c r="K8" s="198"/>
+      <c r="A8" s="172"/>
+      <c r="B8" s="173"/>
+      <c r="C8" s="182"/>
+      <c r="D8" s="178"/>
+      <c r="E8" s="179"/>
+      <c r="F8" s="182"/>
+      <c r="G8" s="178"/>
+      <c r="H8" s="185"/>
+      <c r="I8" s="182"/>
+      <c r="J8" s="199"/>
+      <c r="K8" s="200"/>
     </row>
     <row r="12" spans="1:48">
       <c r="A12" s="110"/>
@@ -4642,13 +4642,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41.25" customHeight="1">
-      <c r="A1" s="242" t="s">
+      <c r="A1" s="244" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="243"/>
-      <c r="C1" s="243"/>
-      <c r="D1" s="243"/>
-      <c r="E1" s="243"/>
+      <c r="B1" s="245"/>
+      <c r="C1" s="245"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="245"/>
     </row>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="46" t="s">
@@ -4690,13 +4690,13 @@
       <c r="E4" s="48"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="245" t="s">
         <v>318</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
-      <c r="D5" s="243"/>
-      <c r="E5" s="243"/>
+      <c r="B5" s="245"/>
+      <c r="C5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="46" t="s">
@@ -4829,14 +4829,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="244" t="s">
+      <c r="A1" s="246" t="s">
         <v>325</v>
       </c>
-      <c r="B1" s="245"/>
-      <c r="C1" s="245"/>
-      <c r="D1" s="245"/>
-      <c r="E1" s="245"/>
-      <c r="F1" s="245"/>
+      <c r="B1" s="247"/>
+      <c r="C1" s="247"/>
+      <c r="D1" s="247"/>
+      <c r="E1" s="247"/>
+      <c r="F1" s="247"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="51" t="s">
@@ -4845,10 +4845,10 @@
       <c r="B2" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="248" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="247"/>
+      <c r="D2" s="249"/>
       <c r="E2" s="51" t="s">
         <v>33</v>
       </c>
@@ -4863,8 +4863,8 @@
       <c r="B3" s="53" t="s">
         <v>326</v>
       </c>
-      <c r="C3" s="248"/>
-      <c r="D3" s="249"/>
+      <c r="C3" s="250"/>
+      <c r="D3" s="251"/>
       <c r="E3" s="53" t="s">
         <v>37</v>
       </c>
@@ -4881,13 +4881,13 @@
       <c r="F4" s="54"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="245" t="s">
+      <c r="A5" s="247" t="s">
         <v>328</v>
       </c>
-      <c r="B5" s="245"/>
-      <c r="C5" s="245"/>
-      <c r="D5" s="245"/>
-      <c r="E5" s="245"/>
+      <c r="B5" s="247"/>
+      <c r="C5" s="247"/>
+      <c r="D5" s="247"/>
+      <c r="E5" s="247"/>
       <c r="F5" s="55"/>
     </row>
     <row r="6" spans="1:6">
@@ -6147,14 +6147,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="250" t="s">
+      <c r="A1" s="252" t="s">
         <v>394</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
+      <c r="B1" s="253"/>
+      <c r="C1" s="253"/>
+      <c r="D1" s="253"/>
+      <c r="E1" s="253"/>
+      <c r="F1" s="253"/>
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="45" t="s">
@@ -6163,10 +6163,10 @@
       <c r="B2" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="253" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="251"/>
+      <c r="D2" s="253"/>
       <c r="E2" s="45" t="s">
         <v>33</v>
       </c>
@@ -6183,13 +6183,13 @@
       <c r="F3" s="60"/>
     </row>
     <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="251" t="s">
+      <c r="A4" s="253" t="s">
         <v>395</v>
       </c>
-      <c r="B4" s="251"/>
-      <c r="C4" s="251"/>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
+      <c r="B4" s="253"/>
+      <c r="C4" s="253"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
       <c r="F4" s="61"/>
     </row>
     <row r="5" spans="1:6" ht="18.75">
@@ -7440,13 +7440,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A1" s="252" t="s">
+      <c r="A1" s="254" t="s">
         <v>397</v>
       </c>
-      <c r="B1" s="253"/>
-      <c r="C1" s="253"/>
-      <c r="D1" s="253"/>
-      <c r="E1" s="253"/>
+      <c r="B1" s="255"/>
+      <c r="C1" s="255"/>
+      <c r="D1" s="255"/>
+      <c r="E1" s="255"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="66" t="s">
@@ -7481,13 +7481,13 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="254" t="s">
+      <c r="A4" s="256" t="s">
         <v>400</v>
       </c>
-      <c r="B4" s="255"/>
-      <c r="C4" s="255"/>
-      <c r="D4" s="255"/>
-      <c r="E4" s="256"/>
+      <c r="B4" s="257"/>
+      <c r="C4" s="257"/>
+      <c r="D4" s="257"/>
+      <c r="E4" s="258"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="66" t="s">
@@ -7603,13 +7603,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="47.25" customHeight="1">
-      <c r="A1" s="257" t="s">
+      <c r="A1" s="259" t="s">
         <v>404</v>
       </c>
-      <c r="B1" s="258"/>
-      <c r="C1" s="258"/>
-      <c r="D1" s="258"/>
-      <c r="E1" s="258"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="70" t="s">
@@ -7636,13 +7636,13 @@
       <c r="E3" s="71"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="251" t="s">
+      <c r="A5" s="253" t="s">
         <v>405</v>
       </c>
-      <c r="B5" s="251"/>
-      <c r="C5" s="251"/>
-      <c r="D5" s="251"/>
-      <c r="E5" s="251"/>
+      <c r="B5" s="253"/>
+      <c r="C5" s="253"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="45" t="s">
@@ -8123,14 +8123,14 @@
       <c r="G12" s="91"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1">
-      <c r="A13" s="259" t="s">
+      <c r="A13" s="166" t="s">
         <v>228</v>
       </c>
-      <c r="B13" s="259"/>
-      <c r="C13" s="259"/>
-      <c r="D13" s="259"/>
-      <c r="E13" s="259"/>
-      <c r="F13" s="260"/>
+      <c r="B13" s="166"/>
+      <c r="C13" s="166"/>
+      <c r="D13" s="166"/>
+      <c r="E13" s="166"/>
+      <c r="F13" s="167"/>
       <c r="G13" s="128"/>
     </row>
     <row r="14" spans="1:7" ht="27">
@@ -8599,15 +8599,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="201" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="201"/>
+      <c r="B1" s="202"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="202"/>
+      <c r="F1" s="202"/>
+      <c r="G1" s="203"/>
       <c r="H1" s="262"/>
     </row>
     <row r="2" spans="1:8">
@@ -8623,11 +8623,11 @@
       <c r="D2" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="200" t="s">
+      <c r="E2" s="202" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="200"/>
-      <c r="G2" s="202"/>
+      <c r="F2" s="202"/>
+      <c r="G2" s="204"/>
       <c r="H2" s="262"/>
     </row>
     <row r="3" spans="1:8">
@@ -8643,9 +8643,9 @@
       <c r="D3" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="203"/>
-      <c r="F3" s="203"/>
-      <c r="G3" s="204"/>
+      <c r="E3" s="205"/>
+      <c r="F3" s="205"/>
+      <c r="G3" s="206"/>
       <c r="H3" s="262"/>
     </row>
     <row r="4" spans="1:8" ht="64.5" customHeight="1">
@@ -8661,23 +8661,23 @@
       <c r="D4" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="203" t="s">
+      <c r="E4" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="203"/>
-      <c r="G4" s="204"/>
+      <c r="F4" s="205"/>
+      <c r="G4" s="206"/>
       <c r="H4" s="262"/>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A5" s="205" t="s">
+      <c r="A5" s="207" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="206"/>
-      <c r="C5" s="206"/>
-      <c r="D5" s="206"/>
-      <c r="E5" s="206"/>
-      <c r="F5" s="206"/>
-      <c r="G5" s="207"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="209"/>
       <c r="H5" s="262"/>
     </row>
     <row r="6" spans="1:8">
@@ -10108,14 +10108,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="208" t="s">
+      <c r="A1" s="210" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="209"/>
-      <c r="C1" s="209"/>
-      <c r="D1" s="209"/>
-      <c r="E1" s="209"/>
-      <c r="F1" s="209"/>
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
@@ -10125,10 +10125,10 @@
       <c r="B2" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="212" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="211"/>
+      <c r="D2" s="213"/>
       <c r="E2" s="25" t="s">
         <v>33</v>
       </c>
@@ -10144,10 +10144,10 @@
       <c r="B3" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="212" t="s">
+      <c r="C3" s="214" t="s">
         <v>174</v>
       </c>
-      <c r="D3" s="213"/>
+      <c r="D3" s="215"/>
       <c r="E3" s="26" t="s">
         <v>37</v>
       </c>
@@ -10163,10 +10163,10 @@
       <c r="B4" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="212" t="s">
+      <c r="C4" s="214" t="s">
         <v>176</v>
       </c>
-      <c r="D4" s="213"/>
+      <c r="D4" s="215"/>
       <c r="E4" s="26" t="s">
         <v>40</v>
       </c>
@@ -10175,14 +10175,14 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="209" t="s">
+      <c r="A5" s="211" t="s">
         <v>178</v>
       </c>
-      <c r="B5" s="209"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="209"/>
-      <c r="E5" s="209"/>
-      <c r="F5" s="209"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="25" t="s">
@@ -10312,14 +10312,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A1" s="214" t="s">
+      <c r="A1" s="216" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="215"/>
-      <c r="C1" s="215"/>
-      <c r="D1" s="215"/>
-      <c r="E1" s="215"/>
-      <c r="F1" s="215"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
     </row>
     <row r="2" spans="1:6" ht="24.75" customHeight="1">
       <c r="A2" s="31" t="s">
@@ -10328,10 +10328,10 @@
       <c r="B2" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="216" t="s">
+      <c r="C2" s="218" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="217"/>
+      <c r="D2" s="219"/>
       <c r="E2" s="31" t="s">
         <v>33</v>
       </c>
@@ -10346,10 +10346,10 @@
       <c r="B3" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="C3" s="218" t="s">
+      <c r="C3" s="220" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="219"/>
+      <c r="D3" s="221"/>
       <c r="E3" s="32" t="s">
         <v>37</v>
       </c>
@@ -10362,10 +10362,10 @@
       <c r="B4" s="35" t="s">
         <v>197</v>
       </c>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="222" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="221"/>
+      <c r="D4" s="223"/>
       <c r="E4" s="34" t="s">
         <v>199</v>
       </c>
@@ -10382,13 +10382,13 @@
       <c r="F5" s="269"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="216" t="s">
+      <c r="A7" s="218" t="s">
         <v>201</v>
       </c>
-      <c r="B7" s="222"/>
-      <c r="C7" s="222"/>
-      <c r="D7" s="222"/>
-      <c r="E7" s="222"/>
+      <c r="B7" s="224"/>
+      <c r="C7" s="224"/>
+      <c r="D7" s="224"/>
+      <c r="E7" s="224"/>
       <c r="F7" s="269"/>
     </row>
     <row r="8" spans="1:6">
@@ -10560,13 +10560,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="225" t="s">
+      <c r="A1" s="227" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="226"/>
-      <c r="C1" s="226"/>
-      <c r="D1" s="226"/>
-      <c r="E1" s="227"/>
+      <c r="B1" s="228"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="229"/>
       <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6">
@@ -10667,39 +10667,39 @@
       <c r="E7" s="16"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
-      <c r="A8" s="225" t="s">
+      <c r="A8" s="227" t="s">
         <v>228</v>
       </c>
-      <c r="B8" s="226"/>
-      <c r="C8" s="226"/>
-      <c r="D8" s="226"/>
-      <c r="E8" s="226"/>
+      <c r="B8" s="228"/>
+      <c r="C8" s="228"/>
+      <c r="D8" s="228"/>
+      <c r="E8" s="228"/>
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="228" t="s">
+      <c r="A9" s="230" t="s">
         <v>229</v>
       </c>
-      <c r="B9" s="229" t="s">
+      <c r="B9" s="231" t="s">
         <v>230</v>
       </c>
-      <c r="C9" s="229" t="s">
+      <c r="C9" s="231" t="s">
         <v>181</v>
       </c>
-      <c r="D9" s="230" t="s">
+      <c r="D9" s="232" t="s">
         <v>182</v>
       </c>
-      <c r="E9" s="230" t="s">
+      <c r="E9" s="232" t="s">
         <v>231</v>
       </c>
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="228"/>
-      <c r="B10" s="229"/>
-      <c r="C10" s="229"/>
-      <c r="D10" s="231"/>
-      <c r="E10" s="231"/>
+      <c r="A10" s="230"/>
+      <c r="B10" s="231"/>
+      <c r="C10" s="231"/>
+      <c r="D10" s="233"/>
+      <c r="E10" s="233"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6">
@@ -11729,13 +11729,13 @@
       <c r="F67" s="5"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="223" t="s">
+      <c r="A68" s="225" t="s">
         <v>248</v>
       </c>
-      <c r="B68" s="224"/>
-      <c r="C68" s="224"/>
-      <c r="D68" s="224"/>
-      <c r="E68" s="224"/>
+      <c r="B68" s="226"/>
+      <c r="C68" s="226"/>
+      <c r="D68" s="226"/>
+      <c r="E68" s="226"/>
       <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6">
@@ -12838,13 +12838,13 @@
       <c r="E4" s="104"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="232" t="s">
+      <c r="A5" s="234" t="s">
         <v>228</v>
       </c>
-      <c r="B5" s="232"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="232"/>
-      <c r="E5" s="232"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="234"/>
+      <c r="D5" s="234"/>
+      <c r="E5" s="234"/>
     </row>
     <row r="6" spans="1:5" ht="30.75">
       <c r="A6" s="134" t="s">
@@ -12971,13 +12971,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="233" t="s">
+      <c r="A1" s="235" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="234"/>
-      <c r="C1" s="234"/>
-      <c r="D1" s="234"/>
-      <c r="E1" s="235"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="237"/>
       <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:6">
@@ -13026,13 +13026,13 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="236" t="s">
+      <c r="A5" s="238" t="s">
         <v>290</v>
       </c>
-      <c r="B5" s="236"/>
-      <c r="C5" s="236"/>
-      <c r="D5" s="236"/>
-      <c r="E5" s="236"/>
+      <c r="B5" s="238"/>
+      <c r="C5" s="238"/>
+      <c r="D5" s="238"/>
+      <c r="E5" s="238"/>
       <c r="F5" s="98"/>
     </row>
     <row r="6" spans="1:6">
@@ -13222,8 +13222,8 @@
       </c>
       <c r="B6" s="43"/>
       <c r="C6" s="43"/>
-      <c r="D6" s="239"/>
-      <c r="E6" s="239"/>
+      <c r="D6" s="241"/>
+      <c r="E6" s="241"/>
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1">
@@ -13236,10 +13236,10 @@
       <c r="C7" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="D7" s="240" t="s">
+      <c r="D7" s="242" t="s">
         <v>182</v>
       </c>
-      <c r="E7" s="241"/>
+      <c r="E7" s="243"/>
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1">
@@ -13252,10 +13252,10 @@
       <c r="C8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="237" t="s">
+      <c r="D8" s="239" t="s">
         <v>305</v>
       </c>
-      <c r="E8" s="238"/>
+      <c r="E8" s="240"/>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1">
@@ -13268,10 +13268,10 @@
       <c r="C9" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="237" t="s">
+      <c r="D9" s="239" t="s">
         <v>118</v>
       </c>
-      <c r="E9" s="238"/>
+      <c r="E9" s="240"/>
       <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" ht="14.45" customHeight="1">
@@ -13284,10 +13284,10 @@
       <c r="C10" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="237" t="s">
+      <c r="D10" s="239" t="s">
         <v>104</v>
       </c>
-      <c r="E10" s="238"/>
+      <c r="E10" s="240"/>
     </row>
     <row r="11" spans="1:7" ht="14.45" customHeight="1">
       <c r="A11" s="8" t="s">
@@ -13299,10 +13299,10 @@
       <c r="C11" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="237" t="s">
+      <c r="D11" s="239" t="s">
         <v>106</v>
       </c>
-      <c r="E11" s="238"/>
+      <c r="E11" s="240"/>
     </row>
     <row r="12" spans="1:7" ht="14.45" customHeight="1">
       <c r="A12" s="8" t="s">
@@ -13314,10 +13314,10 @@
       <c r="C12" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="237" t="s">
+      <c r="D12" s="239" t="s">
         <v>307</v>
       </c>
-      <c r="E12" s="238"/>
+      <c r="E12" s="240"/>
     </row>
     <row r="13" spans="1:7" ht="14.45" customHeight="1">
       <c r="A13" s="8" t="s">
@@ -13329,10 +13329,10 @@
       <c r="C13" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="237" t="s">
+      <c r="D13" s="239" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="238"/>
+      <c r="E13" s="240"/>
     </row>
     <row r="14" spans="1:7" ht="70.5" customHeight="1">
       <c r="A14" s="8" t="s">
@@ -13344,10 +13344,10 @@
       <c r="C14" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="237" t="s">
+      <c r="D14" s="239" t="s">
         <v>309</v>
       </c>
-      <c r="E14" s="238"/>
+      <c r="E14" s="240"/>
     </row>
     <row r="15" spans="1:7" ht="14.45" customHeight="1"/>
   </sheetData>
@@ -13367,6 +13367,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -13538,15 +13547,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -13558,11 +13558,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/input/mapping/002. OCB_GOLD_TCKH_V_BRANCH_LIST_HOP.xlsx
+++ b/input/mapping/002. OCB_GOLD_TCKH_V_BRANCH_LIST_HOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1683" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60F48F75-B12D-4802-9031-45C393D538DB}"/>
+  <xr:revisionPtr revIDLastSave="1692" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{141932BD-C30B-428E-B798-A247274C890D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="15" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -276,8 +276,7 @@
     , 'DIEU CHINH' AS BRANCH_NAME
     , 'VN1000000'  AS BRANCH_CODE
     , 'VN1000000'  AS PRN_BRANCH_CODE
-    , NULL         AS OU_ID
-;</t>
+    , NULL         AS OU_ID</t>
   </si>
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
@@ -290,34 +289,14 @@
     , NVL(dim.PRN_OU_CODE, dim.OU_CODE)     AS PRN_BRANCH_CODE
     , nvl(dim.PRN_OU_NM, dim.OU_NM)       AS PRN_BRANCH_NAME
 FROM CB_OU_DIM dim
-WHERE dim.EFF_TO_DT IS NULL   -- SCD2: chỉ lấy bản ghi còn hiệu lực (NULL = chưa đóng)
-;</t>
+WHERE dim.EFF_TO_DT IS NULL   -- SCD2: chỉ lấy bản ghi còn hiệu lực (NULL = chưa đóng)</t>
   </si>
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS CB_OU_DIM (
-    OU_DIM_ID       BIGINT,     -- MAX(OU_DIM_ID) + ROW_NUMBER()
-    OU_ID           STRING,     -- branch_hashkey (SHA256)
-    OU_NM           STRING,
-    OU_CODE         STRING,
-    PRN_OU_ID       STRING,
-    PRN_OU_NM       STRING,
-    PRN_OU_CODE     STRING,
-    CB_AREA_ID      INTEGER,
-    CB_AREA_NM      STRING,
-    CRT_TM          TIMESTAMP,
-    EFF_FM_DT       DATE,
-    EFF_TO_DT       DATE,
-    START_WK_DT     DATE,
-    OU_ADR          STRING,
-    OU_PH           STRING
-)
-USING DELTA;
 MERGE INTO CB_OU_DIM tgt
 USING (
     WITH
-    -- STS Hub: khóa có trạng thái mới nhất = 'D' (đã xóa) đến :etl_date
     sts_deleted AS (
         SELECT branch_hashkey
         FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_branch')
@@ -325,15 +304,12 @@
         GROUP BY branch_hashkey
         HAVING MAX_BY(cdc_status, source_event_date) = 'D'
     ),
-    -- Hub đang có hiệu lực = Hub LEFT JOIN loại các khóa deleted
     hub_active AS (
         SELECT h.branch_hashkey, h.business_key, h.source_event_date
         FROM IDENTIFIER(:cleaned || '.raw_vault.hub_branch') h
-        LEFT JOIN sts_deleted d
-            ON h.branch_hashkey = d.branch_hashkey
+        LEFT JOIN sts_deleted d ON h.branch_hashkey = d.branch_hashkey
         WHERE d.branch_hashkey IS NULL
     ),
-    -- Satellite (single-active): làm giàu thuộc tính, bản mới nhất đến :etl_date
     sat_latest AS (
         SELECT
             branch_hashkey,
@@ -342,7 +318,6 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- Satellite branch_mapping (single-active)
     bm_latest AS (
         SELECT
             branch_hashkey,
@@ -353,18 +328,23 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
+    area_map AS (
+        SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
+        FROM ou_area_mapping
+        WHERE CB_AREA_ID IS NOT NULL
+    ),
     source_data AS (
         SELECT
-            h.branch_hashkey                                    AS OU_ID,
-            h.business_key                                      AS OU_CODE,
-            SUBSTRING_INDEX(si.t_company_name, '::', 1)         AS OU_NM,
-            prn_hub.branch_hashkey                              AS PRN_OU_ID,
-            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1)     AS PRN_OU_NM,
-            bm.parent_branch_code                               AS PRN_OU_CODE,
+            h.branch_hashkey                                AS OU_ID,
+            h.business_key                                  AS OU_CODE,
+            SUBSTRING_INDEX(si.t_company_name, '::', 1)     AS OU_NM,
+            prn_hub.branch_hashkey                          AS PRN_OU_ID,
+            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1) AS PRN_OU_NM,
+            bm.parent_branch_code                           AS PRN_OU_CODE,
             am.CB_AREA_ID,
             am.CB_AREA_NM,
-            bm.address                                          AS OU_ADR,
-            bm.phone_number                                     AS OU_PH,
+            bm.address                                      AS OU_ADR,
+            bm.phone_number                                 AS OU_PH,
             h.source_event_date
         FROM hub_active h
         LEFT JOIN sat_latest si
@@ -375,15 +355,10 @@
             ON prn_hub.business_key = bm.parent_branch_code
         LEFT JOIN sat_latest prn_si
             ON prn_hub.branch_hashkey = prn_si.branch_hashkey
-        LEFT JOIN ou_area_mapping am
+        LEFT JOIN area_map am
             ON am.OU_ID = h.business_key
         WHERE UPPER(COALESCE(si.t_company_name, '')) &lt;&gt; 'NOT USED'
           AND h.business_key &lt;&gt; 'VN0010001'
-    ),
-    -- Max OU_DIM_ID hiện tại
-    max_id AS (
-        SELECT COALESCE(MAX(OU_DIM_ID), 0) AS max_val
-        FROM CB_OU_DIM
     ),
     changed AS (
         SELECT src.OU_ID
@@ -413,9 +388,8 @@
             src.source_event_date,
             src.OU_ADR,
             src.OU_PH,
-            m.max_val + ROW_NUMBER() OVER (ORDER BY src.OU_ID)  AS NEW_OU_DIM_ID
+            uuid()                                              AS NEW_OU_DIM_ID
         FROM source_data src
-        CROSS JOIN max_id m
         LEFT JOIN CB_OU_DIM tgt_chk
             ON  src.OU_ID        = tgt_chk.OU_ID
             AND tgt_chk.EFF_TO_DT IS NULL
@@ -424,8 +398,8 @@
     ),
     close_records AS (
         SELECT
-            'CLOSE'                                             AS rec_type,
-            'D'                                                 AS CDC_FLAG,
+            'CLOSE'                AS rec_type,
+            'D'                    AS CDC_FLAG,
             tgt.OU_ID,
             tgt.OU_NM,
             tgt.OU_CODE,
@@ -434,10 +408,10 @@
             tgt.PRN_OU_CODE,
             tgt.CB_AREA_ID,
             tgt.CB_AREA_NM,
-            tgt.START_WK_DT                                     AS source_event_date,
+            tgt.START_WK_DT        AS source_event_date,
             tgt.OU_ADR,
             tgt.OU_PH,
-            tgt.OU_DIM_ID                                       AS NEW_OU_DIM_ID
+            tgt.OU_DIM_ID          AS NEW_OU_DIM_ID 
         FROM CB_OU_DIM tgt
         LEFT JOIN source_data src ON src.OU_ID = tgt.OU_ID
         WHERE tgt.EFF_TO_DT IS NULL
@@ -446,9 +420,25 @@
                 OR src.OU_ID IS NULL
               )
     )
-    SELECT * FROM new_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM new_records
     UNION ALL
-    SELECT * FROM close_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM close_records
 ) src
 ON  tgt.OU_ID     = src.OU_ID
 AND tgt.EFF_TO_DT IS NULL
@@ -482,8 +472,7 @@
 WHEN MATCHED AND src.rec_type = 'CLOSE' THEN
     UPDATE SET
         tgt.EFF_TO_DT = DATE_SUB(TO_DATE(:etl_date, 'yyyyMMdd'), 1),
-        tgt.CRT_TM    = CURRENT_TIMESTAMP()
-;</t>
+        tgt.CRT_TM    = CURRENT_TIMESTAMP()</t>
   </si>
   <si>
     <t>JOIN SCHEMA</t>
@@ -3030,7 +3019,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="270">
+  <cellXfs count="271">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3483,290 +3472,293 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="8" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="8" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
@@ -3789,7 +3781,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4158,19 +4150,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="30" customHeight="1">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="184" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
-      <c r="F1" s="187"/>
-      <c r="G1" s="187"/>
-      <c r="H1" s="187"/>
-      <c r="I1" s="187"/>
-      <c r="J1" s="187"/>
-      <c r="K1" s="188"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
+      <c r="J1" s="185"/>
+      <c r="K1" s="186"/>
       <c r="L1" s="24"/>
       <c r="M1" s="24"/>
       <c r="N1" s="24"/>
@@ -4210,157 +4202,157 @@
       <c r="AV1" s="24"/>
     </row>
     <row r="2" spans="1:48" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="168" t="s">
+      <c r="A2" s="166" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="169"/>
-      <c r="C2" s="180" t="s">
+      <c r="B2" s="167"/>
+      <c r="C2" s="178" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="174" t="s">
+      <c r="D2" s="172" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="175"/>
-      <c r="F2" s="180" t="s">
+      <c r="E2" s="173"/>
+      <c r="F2" s="178" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="174" t="s">
+      <c r="G2" s="172" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="183"/>
-      <c r="I2" s="180" t="s">
+      <c r="H2" s="181"/>
+      <c r="I2" s="178" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="189" t="s">
+      <c r="J2" s="187" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="190"/>
+      <c r="K2" s="188"/>
     </row>
     <row r="3" spans="1:48">
-      <c r="A3" s="170"/>
-      <c r="B3" s="171"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="176"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="181"/>
-      <c r="G3" s="176"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="181"/>
-      <c r="J3" s="191"/>
-      <c r="K3" s="192"/>
+      <c r="A3" s="168"/>
+      <c r="B3" s="169"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="174"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="179"/>
+      <c r="G3" s="174"/>
+      <c r="H3" s="182"/>
+      <c r="I3" s="179"/>
+      <c r="J3" s="189"/>
+      <c r="K3" s="190"/>
     </row>
     <row r="4" spans="1:48">
-      <c r="A4" s="170"/>
-      <c r="B4" s="171"/>
-      <c r="C4" s="181"/>
-      <c r="D4" s="176"/>
-      <c r="E4" s="177"/>
-      <c r="F4" s="181"/>
-      <c r="G4" s="176"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="182"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="194"/>
+      <c r="A4" s="168"/>
+      <c r="B4" s="169"/>
+      <c r="C4" s="179"/>
+      <c r="D4" s="174"/>
+      <c r="E4" s="175"/>
+      <c r="F4" s="179"/>
+      <c r="G4" s="174"/>
+      <c r="H4" s="182"/>
+      <c r="I4" s="180"/>
+      <c r="J4" s="191"/>
+      <c r="K4" s="192"/>
     </row>
     <row r="5" spans="1:48">
-      <c r="A5" s="170"/>
-      <c r="B5" s="171"/>
-      <c r="C5" s="181"/>
-      <c r="D5" s="176"/>
-      <c r="E5" s="177"/>
-      <c r="F5" s="181"/>
-      <c r="G5" s="176"/>
-      <c r="H5" s="184"/>
+      <c r="A5" s="168"/>
+      <c r="B5" s="169"/>
+      <c r="C5" s="179"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="175"/>
+      <c r="F5" s="179"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="182"/>
       <c r="J5" s="109"/>
       <c r="K5" s="109"/>
     </row>
     <row r="6" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A6" s="170"/>
-      <c r="B6" s="171"/>
-      <c r="C6" s="181"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="181"/>
-      <c r="G6" s="176"/>
-      <c r="H6" s="184"/>
-      <c r="I6" s="180" t="s">
+      <c r="A6" s="168"/>
+      <c r="B6" s="169"/>
+      <c r="C6" s="179"/>
+      <c r="D6" s="174"/>
+      <c r="E6" s="175"/>
+      <c r="F6" s="179"/>
+      <c r="G6" s="174"/>
+      <c r="H6" s="182"/>
+      <c r="I6" s="178" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="195" t="s">
+      <c r="J6" s="193" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="196"/>
+      <c r="K6" s="194"/>
     </row>
     <row r="7" spans="1:48">
-      <c r="A7" s="170"/>
-      <c r="B7" s="171"/>
-      <c r="C7" s="181"/>
-      <c r="D7" s="176"/>
-      <c r="E7" s="177"/>
-      <c r="F7" s="181"/>
-      <c r="G7" s="176"/>
-      <c r="H7" s="184"/>
-      <c r="I7" s="181"/>
-      <c r="J7" s="197"/>
-      <c r="K7" s="198"/>
+      <c r="A7" s="168"/>
+      <c r="B7" s="169"/>
+      <c r="C7" s="179"/>
+      <c r="D7" s="174"/>
+      <c r="E7" s="175"/>
+      <c r="F7" s="179"/>
+      <c r="G7" s="174"/>
+      <c r="H7" s="182"/>
+      <c r="I7" s="179"/>
+      <c r="J7" s="195"/>
+      <c r="K7" s="196"/>
     </row>
     <row r="8" spans="1:48">
-      <c r="A8" s="172"/>
-      <c r="B8" s="173"/>
-      <c r="C8" s="182"/>
-      <c r="D8" s="178"/>
-      <c r="E8" s="179"/>
-      <c r="F8" s="182"/>
-      <c r="G8" s="178"/>
-      <c r="H8" s="185"/>
-      <c r="I8" s="182"/>
-      <c r="J8" s="199"/>
-      <c r="K8" s="200"/>
+      <c r="A8" s="170"/>
+      <c r="B8" s="171"/>
+      <c r="C8" s="180"/>
+      <c r="D8" s="176"/>
+      <c r="E8" s="177"/>
+      <c r="F8" s="180"/>
+      <c r="G8" s="176"/>
+      <c r="H8" s="183"/>
+      <c r="I8" s="180"/>
+      <c r="J8" s="197"/>
+      <c r="K8" s="198"/>
     </row>
     <row r="12" spans="1:48">
       <c r="A12" s="110"/>
-      <c r="B12" s="261" t="s">
+      <c r="B12" s="262" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="261"/>
-      <c r="D12" s="261"/>
-      <c r="E12" s="261"/>
+      <c r="C12" s="262"/>
+      <c r="D12" s="262"/>
+      <c r="E12" s="262"/>
     </row>
     <row r="13" spans="1:48">
       <c r="A13" s="111"/>
-      <c r="B13" s="261" t="s">
+      <c r="B13" s="262" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="261"/>
-      <c r="D13" s="261"/>
-      <c r="E13" s="261"/>
+      <c r="C13" s="262"/>
+      <c r="D13" s="262"/>
+      <c r="E13" s="262"/>
     </row>
     <row r="14" spans="1:48">
       <c r="A14" s="112"/>
-      <c r="B14" s="261" t="s">
+      <c r="B14" s="262" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="261"/>
-      <c r="D14" s="261"/>
-      <c r="E14" s="261"/>
+      <c r="C14" s="262"/>
+      <c r="D14" s="262"/>
+      <c r="E14" s="262"/>
     </row>
     <row r="15" spans="1:48">
       <c r="A15" s="113"/>
-      <c r="B15" s="261" t="s">
+      <c r="B15" s="262" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="261"/>
-      <c r="D15" s="261"/>
-      <c r="E15" s="261"/>
+      <c r="C15" s="262"/>
+      <c r="D15" s="262"/>
+      <c r="E15" s="262"/>
     </row>
     <row r="16" spans="1:48">
       <c r="A16" s="114"/>
-      <c r="B16" s="261" t="s">
+      <c r="B16" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="261"/>
-      <c r="D16" s="261"/>
-      <c r="E16" s="261"/>
+      <c r="C16" s="262"/>
+      <c r="D16" s="262"/>
+      <c r="E16" s="262"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="115" t="s">
@@ -4642,13 +4634,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41.25" customHeight="1">
-      <c r="A1" s="244" t="s">
+      <c r="A1" s="242" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="245"/>
-      <c r="C1" s="245"/>
-      <c r="D1" s="245"/>
-      <c r="E1" s="245"/>
+      <c r="B1" s="243"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="243"/>
+      <c r="E1" s="243"/>
     </row>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="46" t="s">
@@ -4690,13 +4682,13 @@
       <c r="E4" s="48"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="245" t="s">
+      <c r="A5" s="243" t="s">
         <v>318</v>
       </c>
-      <c r="B5" s="245"/>
-      <c r="C5" s="245"/>
-      <c r="D5" s="245"/>
-      <c r="E5" s="245"/>
+      <c r="B5" s="243"/>
+      <c r="C5" s="243"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="46" t="s">
@@ -4829,14 +4821,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="246" t="s">
+      <c r="A1" s="244" t="s">
         <v>325</v>
       </c>
-      <c r="B1" s="247"/>
-      <c r="C1" s="247"/>
-      <c r="D1" s="247"/>
-      <c r="E1" s="247"/>
-      <c r="F1" s="247"/>
+      <c r="B1" s="245"/>
+      <c r="C1" s="245"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="245"/>
+      <c r="F1" s="245"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="51" t="s">
@@ -4845,10 +4837,10 @@
       <c r="B2" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="246" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="249"/>
+      <c r="D2" s="247"/>
       <c r="E2" s="51" t="s">
         <v>33</v>
       </c>
@@ -4863,8 +4855,8 @@
       <c r="B3" s="53" t="s">
         <v>326</v>
       </c>
-      <c r="C3" s="250"/>
-      <c r="D3" s="251"/>
+      <c r="C3" s="248"/>
+      <c r="D3" s="249"/>
       <c r="E3" s="53" t="s">
         <v>37</v>
       </c>
@@ -4881,13 +4873,13 @@
       <c r="F4" s="54"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="247" t="s">
+      <c r="A5" s="245" t="s">
         <v>328</v>
       </c>
-      <c r="B5" s="247"/>
-      <c r="C5" s="247"/>
-      <c r="D5" s="247"/>
-      <c r="E5" s="247"/>
+      <c r="B5" s="245"/>
+      <c r="C5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
       <c r="F5" s="55"/>
     </row>
     <row r="6" spans="1:6">
@@ -6147,14 +6139,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="252" t="s">
+      <c r="A1" s="250" t="s">
         <v>394</v>
       </c>
-      <c r="B1" s="253"/>
-      <c r="C1" s="253"/>
-      <c r="D1" s="253"/>
-      <c r="E1" s="253"/>
-      <c r="F1" s="253"/>
+      <c r="B1" s="251"/>
+      <c r="C1" s="251"/>
+      <c r="D1" s="251"/>
+      <c r="E1" s="251"/>
+      <c r="F1" s="251"/>
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="45" t="s">
@@ -6163,10 +6155,10 @@
       <c r="B2" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="253" t="s">
+      <c r="C2" s="251" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="253"/>
+      <c r="D2" s="251"/>
       <c r="E2" s="45" t="s">
         <v>33</v>
       </c>
@@ -6183,13 +6175,13 @@
       <c r="F3" s="60"/>
     </row>
     <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="253" t="s">
+      <c r="A4" s="251" t="s">
         <v>395</v>
       </c>
-      <c r="B4" s="253"/>
-      <c r="C4" s="253"/>
-      <c r="D4" s="253"/>
-      <c r="E4" s="253"/>
+      <c r="B4" s="251"/>
+      <c r="C4" s="251"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
       <c r="F4" s="61"/>
     </row>
     <row r="5" spans="1:6" ht="18.75">
@@ -7440,13 +7432,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A1" s="254" t="s">
+      <c r="A1" s="252" t="s">
         <v>397</v>
       </c>
-      <c r="B1" s="255"/>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
-      <c r="E1" s="255"/>
+      <c r="B1" s="253"/>
+      <c r="C1" s="253"/>
+      <c r="D1" s="253"/>
+      <c r="E1" s="253"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="66" t="s">
@@ -7481,13 +7473,13 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="256" t="s">
+      <c r="A4" s="254" t="s">
         <v>400</v>
       </c>
-      <c r="B4" s="257"/>
-      <c r="C4" s="257"/>
-      <c r="D4" s="257"/>
-      <c r="E4" s="258"/>
+      <c r="B4" s="255"/>
+      <c r="C4" s="255"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="256"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="66" t="s">
@@ -7603,13 +7595,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="47.25" customHeight="1">
-      <c r="A1" s="259" t="s">
+      <c r="A1" s="257" t="s">
         <v>404</v>
       </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="258"/>
+      <c r="E1" s="258"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="70" t="s">
@@ -7636,13 +7628,13 @@
       <c r="E3" s="71"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="253" t="s">
+      <c r="A5" s="251" t="s">
         <v>405</v>
       </c>
-      <c r="B5" s="253"/>
-      <c r="C5" s="253"/>
-      <c r="D5" s="253"/>
-      <c r="E5" s="253"/>
+      <c r="B5" s="251"/>
+      <c r="C5" s="251"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="45" t="s">
@@ -8123,14 +8115,14 @@
       <c r="G12" s="91"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1">
-      <c r="A13" s="166" t="s">
+      <c r="A13" s="259" t="s">
         <v>228</v>
       </c>
-      <c r="B13" s="166"/>
-      <c r="C13" s="166"/>
-      <c r="D13" s="166"/>
-      <c r="E13" s="166"/>
-      <c r="F13" s="167"/>
+      <c r="B13" s="259"/>
+      <c r="C13" s="259"/>
+      <c r="D13" s="259"/>
+      <c r="E13" s="259"/>
+      <c r="F13" s="260"/>
       <c r="G13" s="128"/>
     </row>
     <row r="14" spans="1:7" ht="27">
@@ -8556,14 +8548,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" ht="381.75">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="261" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8599,16 +8591,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="201" t="s">
+      <c r="A1" s="199" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="202"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="262"/>
+      <c r="B1" s="200"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="200"/>
+      <c r="G1" s="201"/>
+      <c r="H1" s="263"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="78" t="s">
@@ -8623,12 +8615,12 @@
       <c r="D2" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="202" t="s">
+      <c r="E2" s="200" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="202"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="262"/>
+      <c r="F2" s="200"/>
+      <c r="G2" s="202"/>
+      <c r="H2" s="263"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="75">
@@ -8643,10 +8635,10 @@
       <c r="D3" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="205"/>
-      <c r="F3" s="205"/>
-      <c r="G3" s="206"/>
-      <c r="H3" s="262"/>
+      <c r="E3" s="203"/>
+      <c r="F3" s="203"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="263"/>
     </row>
     <row r="4" spans="1:8" ht="64.5" customHeight="1">
       <c r="A4" s="75">
@@ -8661,24 +8653,24 @@
       <c r="D4" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="205" t="s">
+      <c r="E4" s="203" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="205"/>
-      <c r="G4" s="206"/>
-      <c r="H4" s="262"/>
+      <c r="F4" s="203"/>
+      <c r="G4" s="204"/>
+      <c r="H4" s="263"/>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A5" s="207" t="s">
+      <c r="A5" s="205" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="208"/>
-      <c r="C5" s="208"/>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="262"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="206"/>
+      <c r="E5" s="206"/>
+      <c r="F5" s="206"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="263"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="78" t="s">
@@ -8702,7 +8694,7 @@
       <c r="G6" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="262"/>
+      <c r="H6" s="263"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="75">
@@ -8726,7 +8718,7 @@
       <c r="G7" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="262"/>
+      <c r="H7" s="263"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="75">
@@ -8750,7 +8742,7 @@
       <c r="G8" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H8" s="262"/>
+      <c r="H8" s="263"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="75">
@@ -8774,7 +8766,7 @@
       <c r="G9" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="262"/>
+      <c r="H9" s="263"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="75">
@@ -8798,7 +8790,7 @@
       <c r="G10" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="262"/>
+      <c r="H10" s="263"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="75">
@@ -8822,7 +8814,7 @@
       <c r="G11" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="262"/>
+      <c r="H11" s="263"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="75">
@@ -8846,7 +8838,7 @@
       <c r="G12" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H12" s="262"/>
+      <c r="H12" s="263"/>
     </row>
     <row r="13" spans="1:8" ht="60.75">
       <c r="A13" s="75">
@@ -8870,7 +8862,7 @@
       <c r="G13" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="H13" s="262"/>
+      <c r="H13" s="263"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="75">
@@ -8894,7 +8886,7 @@
       <c r="G14" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H14" s="262"/>
+      <c r="H14" s="263"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="75">
@@ -8918,7 +8910,7 @@
       <c r="G15" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="262"/>
+      <c r="H15" s="263"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="75">
@@ -8942,7 +8934,7 @@
       <c r="G16" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="262"/>
+      <c r="H16" s="263"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="75">
@@ -8966,7 +8958,7 @@
       <c r="G17" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H17" s="262"/>
+      <c r="H17" s="263"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="75">
@@ -8990,7 +8982,7 @@
       <c r="G18" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H18" s="262"/>
+      <c r="H18" s="263"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="75">
@@ -9014,7 +9006,7 @@
       <c r="G19" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="262"/>
+      <c r="H19" s="263"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="75">
@@ -9038,7 +9030,7 @@
       <c r="G20" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H20" s="262"/>
+      <c r="H20" s="263"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="75">
@@ -9062,7 +9054,7 @@
       <c r="G21" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H21" s="262"/>
+      <c r="H21" s="263"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="75">
@@ -9086,7 +9078,7 @@
       <c r="G22" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H22" s="262"/>
+      <c r="H22" s="263"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="75">
@@ -9110,7 +9102,7 @@
       <c r="G23" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H23" s="262"/>
+      <c r="H23" s="263"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="75">
@@ -9134,7 +9126,7 @@
       <c r="G24" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H24" s="262"/>
+      <c r="H24" s="263"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="75">
@@ -9158,7 +9150,7 @@
       <c r="G25" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H25" s="262"/>
+      <c r="H25" s="263"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="75">
@@ -9182,7 +9174,7 @@
       <c r="G26" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H26" s="262"/>
+      <c r="H26" s="263"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="75">
@@ -9206,7 +9198,7 @@
       <c r="G27" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H27" s="262"/>
+      <c r="H27" s="263"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="75">
@@ -9230,7 +9222,7 @@
       <c r="G28" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H28" s="262"/>
+      <c r="H28" s="263"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="75">
@@ -9254,7 +9246,7 @@
       <c r="G29" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H29" s="262"/>
+      <c r="H29" s="263"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="75">
@@ -9278,7 +9270,7 @@
       <c r="G30" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H30" s="262"/>
+      <c r="H30" s="263"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="75">
@@ -9302,7 +9294,7 @@
       <c r="G31" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H31" s="262"/>
+      <c r="H31" s="263"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="75">
@@ -9326,7 +9318,7 @@
       <c r="G32" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H32" s="262"/>
+      <c r="H32" s="263"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="75">
@@ -9350,7 +9342,7 @@
       <c r="G33" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H33" s="262"/>
+      <c r="H33" s="263"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="75">
@@ -9374,7 +9366,7 @@
       <c r="G34" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H34" s="262"/>
+      <c r="H34" s="263"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="75">
@@ -9398,7 +9390,7 @@
       <c r="G35" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H35" s="262"/>
+      <c r="H35" s="263"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="75">
@@ -9422,7 +9414,7 @@
       <c r="G36" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H36" s="262"/>
+      <c r="H36" s="263"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="75">
@@ -9446,7 +9438,7 @@
       <c r="G37" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H37" s="262"/>
+      <c r="H37" s="263"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="75">
@@ -9470,7 +9462,7 @@
       <c r="G38" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H38" s="262"/>
+      <c r="H38" s="263"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="75">
@@ -9494,7 +9486,7 @@
       <c r="G39" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H39" s="262"/>
+      <c r="H39" s="263"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="75">
@@ -9518,7 +9510,7 @@
       <c r="G40" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H40" s="262"/>
+      <c r="H40" s="263"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="75">
@@ -9542,7 +9534,7 @@
       <c r="G41" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H41" s="262"/>
+      <c r="H41" s="263"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="75">
@@ -9566,7 +9558,7 @@
       <c r="G42" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H42" s="262"/>
+      <c r="H42" s="263"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="75">
@@ -9590,7 +9582,7 @@
       <c r="G43" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H43" s="262"/>
+      <c r="H43" s="263"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="75">
@@ -9614,7 +9606,7 @@
       <c r="G44" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H44" s="262"/>
+      <c r="H44" s="263"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="75">
@@ -9638,7 +9630,7 @@
       <c r="G45" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H45" s="262"/>
+      <c r="H45" s="263"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="75">
@@ -9662,7 +9654,7 @@
       <c r="G46" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H46" s="262"/>
+      <c r="H46" s="263"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="75">
@@ -9686,7 +9678,7 @@
       <c r="G47" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H47" s="262"/>
+      <c r="H47" s="263"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="75">
@@ -9710,7 +9702,7 @@
       <c r="G48" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H48" s="262"/>
+      <c r="H48" s="263"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="75">
@@ -9734,7 +9726,7 @@
       <c r="G49" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H49" s="262"/>
+      <c r="H49" s="263"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="75">
@@ -9758,7 +9750,7 @@
       <c r="G50" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H50" s="262"/>
+      <c r="H50" s="263"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="75">
@@ -9782,7 +9774,7 @@
       <c r="G51" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H51" s="262"/>
+      <c r="H51" s="263"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="75">
@@ -9806,7 +9798,7 @@
       <c r="G52" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H52" s="262"/>
+      <c r="H52" s="263"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="75">
@@ -9830,7 +9822,7 @@
       <c r="G53" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H53" s="262"/>
+      <c r="H53" s="263"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="75">
@@ -9854,7 +9846,7 @@
       <c r="G54" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H54" s="262"/>
+      <c r="H54" s="263"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="75">
@@ -9878,7 +9870,7 @@
       <c r="G55" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H55" s="262"/>
+      <c r="H55" s="263"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="75">
@@ -9902,7 +9894,7 @@
       <c r="G56" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H56" s="262"/>
+      <c r="H56" s="263"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="75">
@@ -9926,7 +9918,7 @@
       <c r="G57" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="H57" s="262"/>
+      <c r="H57" s="263"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="106">
@@ -9950,137 +9942,137 @@
       <c r="G58" s="107" t="s">
         <v>54</v>
       </c>
-      <c r="H58" s="262"/>
+      <c r="H58" s="263"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="263">
+      <c r="A59" s="264">
         <v>53</v>
       </c>
-      <c r="B59" s="264" t="s">
+      <c r="B59" s="265" t="s">
         <v>49</v>
       </c>
-      <c r="C59" s="265" t="s">
+      <c r="C59" s="266" t="s">
         <v>162</v>
       </c>
-      <c r="D59" s="266" t="s">
+      <c r="D59" s="267" t="s">
         <v>51</v>
       </c>
-      <c r="E59" s="267" t="s">
-        <v>52</v>
-      </c>
-      <c r="F59" s="264" t="s">
+      <c r="E59" s="268" t="s">
+        <v>52</v>
+      </c>
+      <c r="F59" s="265" t="s">
         <v>163</v>
       </c>
-      <c r="G59" s="264" t="s">
+      <c r="G59" s="265" t="s">
         <v>54</v>
       </c>
-      <c r="H59" s="262"/>
+      <c r="H59" s="263"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="263">
+      <c r="A60" s="264">
         <v>54</v>
       </c>
-      <c r="B60" s="264" t="s">
+      <c r="B60" s="265" t="s">
         <v>49</v>
       </c>
-      <c r="C60" s="265" t="s">
+      <c r="C60" s="266" t="s">
         <v>164</v>
       </c>
-      <c r="D60" s="266" t="s">
+      <c r="D60" s="267" t="s">
         <v>51</v>
       </c>
-      <c r="E60" s="267" t="s">
-        <v>52</v>
-      </c>
-      <c r="F60" s="264" t="s">
+      <c r="E60" s="268" t="s">
+        <v>52</v>
+      </c>
+      <c r="F60" s="265" t="s">
         <v>165</v>
       </c>
-      <c r="G60" s="264" t="s">
+      <c r="G60" s="265" t="s">
         <v>54</v>
       </c>
-      <c r="H60" s="262"/>
+      <c r="H60" s="263"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="263">
+      <c r="A61" s="264">
         <v>55</v>
       </c>
-      <c r="B61" s="264" t="s">
+      <c r="B61" s="265" t="s">
         <v>49</v>
       </c>
-      <c r="C61" s="265" t="s">
+      <c r="C61" s="266" t="s">
         <v>166</v>
       </c>
-      <c r="D61" s="266" t="s">
+      <c r="D61" s="267" t="s">
         <v>51</v>
       </c>
-      <c r="E61" s="267" t="s">
-        <v>52</v>
-      </c>
-      <c r="F61" s="264" t="s">
+      <c r="E61" s="268" t="s">
+        <v>52</v>
+      </c>
+      <c r="F61" s="265" t="s">
         <v>167</v>
       </c>
-      <c r="G61" s="264" t="s">
+      <c r="G61" s="265" t="s">
         <v>54</v>
       </c>
-      <c r="H61" s="262"/>
+      <c r="H61" s="263"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="263">
+      <c r="A62" s="264">
         <v>56</v>
       </c>
-      <c r="B62" s="264" t="s">
+      <c r="B62" s="265" t="s">
         <v>49</v>
       </c>
-      <c r="C62" s="265" t="s">
+      <c r="C62" s="266" t="s">
         <v>168</v>
       </c>
-      <c r="D62" s="266" t="s">
+      <c r="D62" s="267" t="s">
         <v>84</v>
       </c>
-      <c r="E62" s="267" t="s">
-        <v>52</v>
-      </c>
-      <c r="F62" s="264" t="s">
+      <c r="E62" s="268" t="s">
+        <v>52</v>
+      </c>
+      <c r="F62" s="265" t="s">
         <v>169</v>
       </c>
-      <c r="G62" s="264" t="s">
+      <c r="G62" s="265" t="s">
         <v>54</v>
       </c>
-      <c r="H62" s="262"/>
+      <c r="H62" s="263"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="263">
+      <c r="A63" s="264">
         <v>57</v>
       </c>
-      <c r="B63" s="264" t="s">
+      <c r="B63" s="265" t="s">
         <v>49</v>
       </c>
-      <c r="C63" s="265" t="s">
+      <c r="C63" s="266" t="s">
         <v>170</v>
       </c>
-      <c r="D63" s="266" t="s">
+      <c r="D63" s="267" t="s">
         <v>51</v>
       </c>
-      <c r="E63" s="267" t="s">
-        <v>52</v>
-      </c>
-      <c r="F63" s="264" t="s">
+      <c r="E63" s="268" t="s">
+        <v>52</v>
+      </c>
+      <c r="F63" s="265" t="s">
         <v>171</v>
       </c>
-      <c r="G63" s="264" t="s">
+      <c r="G63" s="265" t="s">
         <v>54</v>
       </c>
-      <c r="H63" s="262"/>
+      <c r="H63" s="263"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="268"/>
-      <c r="B64" s="262"/>
-      <c r="C64" s="268"/>
-      <c r="D64" s="268"/>
-      <c r="E64" s="262"/>
-      <c r="F64" s="262"/>
-      <c r="G64" s="262"/>
-      <c r="H64" s="269"/>
+      <c r="A64" s="269"/>
+      <c r="B64" s="263"/>
+      <c r="C64" s="269"/>
+      <c r="D64" s="269"/>
+      <c r="E64" s="263"/>
+      <c r="F64" s="263"/>
+      <c r="G64" s="263"/>
+      <c r="H64" s="270"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10108,14 +10100,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="208" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
+      <c r="B1" s="209"/>
+      <c r="C1" s="209"/>
+      <c r="D1" s="209"/>
+      <c r="E1" s="209"/>
+      <c r="F1" s="209"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
@@ -10125,10 +10117,10 @@
       <c r="B2" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="210" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="213"/>
+      <c r="D2" s="211"/>
       <c r="E2" s="25" t="s">
         <v>33</v>
       </c>
@@ -10144,10 +10136,10 @@
       <c r="B3" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="214" t="s">
+      <c r="C3" s="212" t="s">
         <v>174</v>
       </c>
-      <c r="D3" s="215"/>
+      <c r="D3" s="213"/>
       <c r="E3" s="26" t="s">
         <v>37</v>
       </c>
@@ -10163,10 +10155,10 @@
       <c r="B4" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="214" t="s">
+      <c r="C4" s="212" t="s">
         <v>176</v>
       </c>
-      <c r="D4" s="215"/>
+      <c r="D4" s="213"/>
       <c r="E4" s="26" t="s">
         <v>40</v>
       </c>
@@ -10175,14 +10167,14 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="211" t="s">
+      <c r="A5" s="209" t="s">
         <v>178</v>
       </c>
-      <c r="B5" s="211"/>
-      <c r="C5" s="211"/>
-      <c r="D5" s="211"/>
-      <c r="E5" s="211"/>
-      <c r="F5" s="211"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
+      <c r="F5" s="209"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="25" t="s">
@@ -10312,14 +10304,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A1" s="216" t="s">
+      <c r="A1" s="214" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="217"/>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="217"/>
+      <c r="B1" s="215"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="215"/>
     </row>
     <row r="2" spans="1:6" ht="24.75" customHeight="1">
       <c r="A2" s="31" t="s">
@@ -10328,10 +10320,10 @@
       <c r="B2" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="218" t="s">
+      <c r="C2" s="216" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="219"/>
+      <c r="D2" s="217"/>
       <c r="E2" s="31" t="s">
         <v>33</v>
       </c>
@@ -10346,10 +10338,10 @@
       <c r="B3" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="C3" s="220" t="s">
+      <c r="C3" s="218" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="221"/>
+      <c r="D3" s="219"/>
       <c r="E3" s="32" t="s">
         <v>37</v>
       </c>
@@ -10362,10 +10354,10 @@
       <c r="B4" s="35" t="s">
         <v>197</v>
       </c>
-      <c r="C4" s="222" t="s">
+      <c r="C4" s="220" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="223"/>
+      <c r="D4" s="221"/>
       <c r="E4" s="34" t="s">
         <v>199</v>
       </c>
@@ -10374,22 +10366,22 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A5" s="269"/>
-      <c r="B5" s="269"/>
-      <c r="C5" s="269"/>
-      <c r="D5" s="269"/>
-      <c r="E5" s="269"/>
-      <c r="F5" s="269"/>
+      <c r="A5" s="270"/>
+      <c r="B5" s="270"/>
+      <c r="C5" s="270"/>
+      <c r="D5" s="270"/>
+      <c r="E5" s="270"/>
+      <c r="F5" s="270"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="218" t="s">
+      <c r="A7" s="216" t="s">
         <v>201</v>
       </c>
-      <c r="B7" s="224"/>
-      <c r="C7" s="224"/>
-      <c r="D7" s="224"/>
-      <c r="E7" s="224"/>
-      <c r="F7" s="269"/>
+      <c r="B7" s="222"/>
+      <c r="C7" s="222"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="222"/>
+      <c r="F7" s="270"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="31" t="s">
@@ -10407,7 +10399,7 @@
       <c r="E8" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="F8" s="269"/>
+      <c r="F8" s="270"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="36" t="s">
@@ -10425,7 +10417,7 @@
       <c r="E9" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="F9" s="269"/>
+      <c r="F9" s="270"/>
     </row>
     <row r="10" spans="1:6" ht="60.75">
       <c r="A10" s="36" t="s">
@@ -10443,7 +10435,7 @@
       <c r="E10" s="39" t="s">
         <v>205</v>
       </c>
-      <c r="F10" s="269"/>
+      <c r="F10" s="270"/>
     </row>
     <row r="11" spans="1:6" ht="91.5">
       <c r="A11" s="36" t="s">
@@ -10461,7 +10453,7 @@
       <c r="E11" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="F11" s="269"/>
+      <c r="F11" s="270"/>
     </row>
     <row r="12" spans="1:6" ht="121.5">
       <c r="A12" s="36" t="s">
@@ -10479,7 +10471,7 @@
       <c r="E12" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="F12" s="269"/>
+      <c r="F12" s="270"/>
     </row>
     <row r="13" spans="1:6" ht="76.5">
       <c r="A13" s="36" t="s">
@@ -10497,7 +10489,7 @@
       <c r="E13" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="F13" s="269"/>
+      <c r="F13" s="270"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="36" t="s">
@@ -10515,7 +10507,7 @@
       <c r="E14" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="F14" s="269"/>
+      <c r="F14" s="270"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="36" t="s">
@@ -10533,7 +10525,7 @@
       <c r="E15" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="F15" s="269"/>
+      <c r="F15" s="270"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10560,13 +10552,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="227" t="s">
+      <c r="A1" s="225" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="228"/>
-      <c r="C1" s="228"/>
-      <c r="D1" s="228"/>
-      <c r="E1" s="229"/>
+      <c r="B1" s="226"/>
+      <c r="C1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="227"/>
       <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6">
@@ -10667,39 +10659,39 @@
       <c r="E7" s="16"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
-      <c r="A8" s="227" t="s">
+      <c r="A8" s="225" t="s">
         <v>228</v>
       </c>
-      <c r="B8" s="228"/>
-      <c r="C8" s="228"/>
-      <c r="D8" s="228"/>
-      <c r="E8" s="228"/>
+      <c r="B8" s="226"/>
+      <c r="C8" s="226"/>
+      <c r="D8" s="226"/>
+      <c r="E8" s="226"/>
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="230" t="s">
+      <c r="A9" s="228" t="s">
         <v>229</v>
       </c>
-      <c r="B9" s="231" t="s">
+      <c r="B9" s="229" t="s">
         <v>230</v>
       </c>
-      <c r="C9" s="231" t="s">
+      <c r="C9" s="229" t="s">
         <v>181</v>
       </c>
-      <c r="D9" s="232" t="s">
+      <c r="D9" s="230" t="s">
         <v>182</v>
       </c>
-      <c r="E9" s="232" t="s">
+      <c r="E9" s="230" t="s">
         <v>231</v>
       </c>
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="230"/>
-      <c r="B10" s="231"/>
-      <c r="C10" s="231"/>
-      <c r="D10" s="233"/>
-      <c r="E10" s="233"/>
+      <c r="A10" s="228"/>
+      <c r="B10" s="229"/>
+      <c r="C10" s="229"/>
+      <c r="D10" s="231"/>
+      <c r="E10" s="231"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6">
@@ -11729,13 +11721,13 @@
       <c r="F67" s="5"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="225" t="s">
+      <c r="A68" s="223" t="s">
         <v>248</v>
       </c>
-      <c r="B68" s="226"/>
-      <c r="C68" s="226"/>
-      <c r="D68" s="226"/>
-      <c r="E68" s="226"/>
+      <c r="B68" s="224"/>
+      <c r="C68" s="224"/>
+      <c r="D68" s="224"/>
+      <c r="E68" s="224"/>
       <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6">
@@ -12838,13 +12830,13 @@
       <c r="E4" s="104"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="234" t="s">
+      <c r="A5" s="232" t="s">
         <v>228</v>
       </c>
-      <c r="B5" s="234"/>
-      <c r="C5" s="234"/>
-      <c r="D5" s="234"/>
-      <c r="E5" s="234"/>
+      <c r="B5" s="232"/>
+      <c r="C5" s="232"/>
+      <c r="D5" s="232"/>
+      <c r="E5" s="232"/>
     </row>
     <row r="6" spans="1:5" ht="30.75">
       <c r="A6" s="134" t="s">
@@ -12971,13 +12963,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="235" t="s">
+      <c r="A1" s="233" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="237"/>
+      <c r="B1" s="234"/>
+      <c r="C1" s="234"/>
+      <c r="D1" s="234"/>
+      <c r="E1" s="235"/>
       <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:6">
@@ -13026,13 +13018,13 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="238" t="s">
+      <c r="A5" s="236" t="s">
         <v>290</v>
       </c>
-      <c r="B5" s="238"/>
-      <c r="C5" s="238"/>
-      <c r="D5" s="238"/>
-      <c r="E5" s="238"/>
+      <c r="B5" s="236"/>
+      <c r="C5" s="236"/>
+      <c r="D5" s="236"/>
+      <c r="E5" s="236"/>
       <c r="F5" s="98"/>
     </row>
     <row r="6" spans="1:6">
@@ -13222,8 +13214,8 @@
       </c>
       <c r="B6" s="43"/>
       <c r="C6" s="43"/>
-      <c r="D6" s="241"/>
-      <c r="E6" s="241"/>
+      <c r="D6" s="239"/>
+      <c r="E6" s="239"/>
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1">
@@ -13236,10 +13228,10 @@
       <c r="C7" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="D7" s="242" t="s">
+      <c r="D7" s="240" t="s">
         <v>182</v>
       </c>
-      <c r="E7" s="243"/>
+      <c r="E7" s="241"/>
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1">
@@ -13252,10 +13244,10 @@
       <c r="C8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="239" t="s">
+      <c r="D8" s="237" t="s">
         <v>305</v>
       </c>
-      <c r="E8" s="240"/>
+      <c r="E8" s="238"/>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1">
@@ -13268,10 +13260,10 @@
       <c r="C9" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="239" t="s">
+      <c r="D9" s="237" t="s">
         <v>118</v>
       </c>
-      <c r="E9" s="240"/>
+      <c r="E9" s="238"/>
       <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" ht="14.45" customHeight="1">
@@ -13284,10 +13276,10 @@
       <c r="C10" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="239" t="s">
+      <c r="D10" s="237" t="s">
         <v>104</v>
       </c>
-      <c r="E10" s="240"/>
+      <c r="E10" s="238"/>
     </row>
     <row r="11" spans="1:7" ht="14.45" customHeight="1">
       <c r="A11" s="8" t="s">
@@ -13299,10 +13291,10 @@
       <c r="C11" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="239" t="s">
+      <c r="D11" s="237" t="s">
         <v>106</v>
       </c>
-      <c r="E11" s="240"/>
+      <c r="E11" s="238"/>
     </row>
     <row r="12" spans="1:7" ht="14.45" customHeight="1">
       <c r="A12" s="8" t="s">
@@ -13314,10 +13306,10 @@
       <c r="C12" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="239" t="s">
+      <c r="D12" s="237" t="s">
         <v>307</v>
       </c>
-      <c r="E12" s="240"/>
+      <c r="E12" s="238"/>
     </row>
     <row r="13" spans="1:7" ht="14.45" customHeight="1">
       <c r="A13" s="8" t="s">
@@ -13329,10 +13321,10 @@
       <c r="C13" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="239" t="s">
+      <c r="D13" s="237" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="240"/>
+      <c r="E13" s="238"/>
     </row>
     <row r="14" spans="1:7" ht="70.5" customHeight="1">
       <c r="A14" s="8" t="s">
@@ -13344,10 +13336,10 @@
       <c r="C14" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="239" t="s">
+      <c r="D14" s="237" t="s">
         <v>309</v>
       </c>
-      <c r="E14" s="240"/>
+      <c r="E14" s="238"/>
     </row>
     <row r="15" spans="1:7" ht="14.45" customHeight="1"/>
   </sheetData>
@@ -13367,15 +13359,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -13547,7 +13530,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
@@ -13557,14 +13540,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
 </file>